--- a/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
@@ -18,31 +18,31 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:si>
+    <x:t>(5,5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(4,5)</x:t>
+  </x:si>
+  <x:si>
     <x:t>(3,5)</x:t>
   </x:si>
   <x:si>
-    <x:t>(4,5)</x:t>
+    <x:t>(6,5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(7,5)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(5,4)</x:t>
   </x:si>
   <x:si>
     <x:t>(5,3)</x:t>
   </x:si>
   <x:si>
-    <x:t>(5,4)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(5,5)</x:t>
-  </x:si>
-  <x:si>
     <x:t>(5,6)</x:t>
   </x:si>
   <x:si>
     <x:t>(5,7)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(6,5)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(7,5)</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -458,7 +458,7 @@
   <x:sheetData>
     <x:row r="3" spans="1:7">
       <x:c r="E3" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
@@ -468,29 +468,29 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="C5" s="2" t="s">
-        <x:v>2</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="G5" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="E6" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="E7" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
@@ -450,9 +450,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:G7"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -473,7 +470,7 @@
       <x:c r="D5" s="2" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E5" s="0" t="s">
+      <x:c r="E5" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="3" t="s">
@@ -494,19 +491,12 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:D12"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
@@ -535,27 +525,20 @@
       <x:c r="D12" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1:L4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="1" customWidth="1"/>
-    <x:col min="2" max="2" width="9.140625" style="4" customWidth="1"/>
-    <x:col min="3" max="3" width="9.140625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.140625" style="5" customWidth="1"/>
-    <x:col min="5" max="5" width="9.140625" style="3" customWidth="1"/>
+    <x:col min="1" max="1" width="9.140625" style="1"/>
+    <x:col min="2" max="2" width="9.140625" style="4"/>
+    <x:col min="3" max="3" width="9.140625"/>
+    <x:col min="4" max="4" width="9.140625" style="5"/>
+    <x:col min="5" max="5" width="9.140625" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:12">
@@ -577,10 +560,6 @@
       <x:c r="L4" s="3"/>
     </x:row>
   </x:sheetData>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
+++ b/XLibur.Tests/Resource/Examples/Ranges/WalkingRanges.xlsx
@@ -534,11 +534,11 @@
   <x:dimension ref="A1:L4"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="9.140625" style="1"/>
-    <x:col min="2" max="2" width="9.140625" style="4"/>
-    <x:col min="3" max="3" width="9.140625"/>
-    <x:col min="4" max="4" width="9.140625" style="5"/>
-    <x:col min="5" max="5" width="9.140625" style="3"/>
+    <x:col min="1" max="1" width="9.144286" style="1"/>
+    <x:col min="2" max="2" width="9.144286" style="4"/>
+    <x:col min="3" max="3" width="9.144286"/>
+    <x:col min="4" max="4" width="9.144286" style="5"/>
+    <x:col min="5" max="5" width="9.144286" style="3"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:12">
